--- a/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N91_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3211_W0021F0003T0006Z000C1N91_analysis.xlsx
@@ -480,10 +480,10 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>6.412371775537703</v>
+        <v>1.042010413524877</v>
       </c>
       <c r="D2" t="n">
-        <v>6.647256915519064</v>
+        <v>1.080179248771848</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
